--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3223,6 +3223,3228 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120472650</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>514823</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7128562</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120471334</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>514745</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7128436</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120473051</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514862</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7128700</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120471120</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>514749</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7128456</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120473466</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Grundsundet, Grundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>514969</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7128668</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120471208</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>514759</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7128445</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120473036</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>514863</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7128699</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120472732</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>514834</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7128590</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120472288</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>514859</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7128434</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120471187</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>514760</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7128455</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120471298</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91370</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>514758</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7128446</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120471013</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>514711</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7128463</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120473043</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>514860</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7128698</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120473441</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grundsundet, Grundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>514964</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7128671</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120471864</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>514759</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7128395</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120473819</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grundsundet, Grundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>515087</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7128729</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120473868</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grundsundet, Grundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>515087</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7128736</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120473146</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>514877</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7128689</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120473800</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grundsundet, Grundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>515084</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7128716</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120472276</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>514855</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7128420</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120472115</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>514793</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7128431</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120471937</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>514784</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7128441</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120471856</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>514760</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7128399</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120471315</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>514757</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7128439</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120472156</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78279</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>514822</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7128428</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120473097</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>514881</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7128694</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120473133</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>514883</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7128696</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120471114</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>514743</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7128447</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120471755</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>514726</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7128427</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120471204</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>514761</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7128451</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120473562</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Grundsundet, Grundsundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>515029</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7128693</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -3225,10 +3225,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120472650</v>
+        <v>120473051</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3237,20 +3237,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514823</v>
+        <v>514862</v>
       </c>
       <c r="R22" t="n">
-        <v>7128562</v>
+        <v>7128700</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120471334</v>
+        <v>120473800</v>
       </c>
       <c r="B23" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3343,37 +3343,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514745</v>
+        <v>515084</v>
       </c>
       <c r="R23" t="n">
-        <v>7128436</v>
+        <v>7128716</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3403,6 +3408,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3429,10 +3439,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120473051</v>
+        <v>120471864</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3441,25 +3451,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514862</v>
+        <v>514759</v>
       </c>
       <c r="R24" t="n">
-        <v>7128700</v>
+        <v>7128395</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3531,10 +3541,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120471120</v>
+        <v>120471114</v>
       </c>
       <c r="B25" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3543,25 +3553,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3571,10 +3581,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514749</v>
+        <v>514743</v>
       </c>
       <c r="R25" t="n">
-        <v>7128456</v>
+        <v>7128447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3633,10 +3643,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120473466</v>
+        <v>120473819</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3649,21 +3659,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3673,13 +3683,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514969</v>
+        <v>515087</v>
       </c>
       <c r="R26" t="n">
-        <v>7128668</v>
+        <v>7128729</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3709,6 +3719,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3735,10 +3750,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120471208</v>
+        <v>120472288</v>
       </c>
       <c r="B27" t="n">
-        <v>79658</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3747,25 +3762,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3775,13 +3790,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514759</v>
+        <v>514859</v>
       </c>
       <c r="R27" t="n">
-        <v>7128445</v>
+        <v>7128434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3811,6 +3826,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3837,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120473036</v>
+        <v>120473133</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3853,21 +3873,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3877,10 +3897,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514863</v>
+        <v>514883</v>
       </c>
       <c r="R28" t="n">
-        <v>7128699</v>
+        <v>7128696</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3913,6 +3933,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3939,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120472732</v>
+        <v>120471208</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79658</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3951,43 +3976,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514834</v>
+        <v>514759</v>
       </c>
       <c r="R29" t="n">
-        <v>7128590</v>
+        <v>7128445</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4020,11 +4040,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4051,10 +4066,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120472288</v>
+        <v>120472156</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4067,21 +4082,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4091,10 +4106,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514859</v>
+        <v>514822</v>
       </c>
       <c r="R30" t="n">
-        <v>7128434</v>
+        <v>7128428</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4127,11 +4142,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4158,10 +4168,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120471187</v>
+        <v>120473441</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4174,34 +4184,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514760</v>
+        <v>514964</v>
       </c>
       <c r="R31" t="n">
-        <v>7128455</v>
+        <v>7128671</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4234,6 +4244,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4260,10 +4275,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120471298</v>
+        <v>120473146</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>79624</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4276,21 +4291,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2014</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4300,13 +4315,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514758</v>
+        <v>514877</v>
       </c>
       <c r="R32" t="n">
-        <v>7128446</v>
+        <v>7128689</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4362,10 +4377,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120471013</v>
+        <v>120473562</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4378,34 +4393,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514711</v>
+        <v>515029</v>
       </c>
       <c r="R33" t="n">
-        <v>7128463</v>
+        <v>7128693</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4438,6 +4453,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4464,10 +4484,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120473043</v>
+        <v>120471187</v>
       </c>
       <c r="B34" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4480,21 +4500,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4504,13 +4524,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514860</v>
+        <v>514760</v>
       </c>
       <c r="R34" t="n">
-        <v>7128698</v>
+        <v>7128455</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4566,7 +4586,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120473441</v>
+        <v>120472276</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4602,14 +4622,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514964</v>
+        <v>514855</v>
       </c>
       <c r="R35" t="n">
-        <v>7128671</v>
+        <v>7128420</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4673,10 +4693,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120471864</v>
+        <v>120471315</v>
       </c>
       <c r="B36" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4689,37 +4709,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514759</v>
+        <v>514757</v>
       </c>
       <c r="R36" t="n">
-        <v>7128395</v>
+        <v>7128439</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4775,10 +4800,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120473819</v>
+        <v>120472115</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4787,41 +4812,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515087</v>
+        <v>514793</v>
       </c>
       <c r="R37" t="n">
-        <v>7128729</v>
+        <v>7128431</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4851,11 +4876,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4882,10 +4902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120473868</v>
+        <v>120471204</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4894,41 +4914,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515087</v>
+        <v>514761</v>
       </c>
       <c r="R38" t="n">
-        <v>7128736</v>
+        <v>7128451</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4958,11 +4978,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4989,7 +5004,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473146</v>
+        <v>120473097</v>
       </c>
       <c r="B39" t="n">
         <v>79624</v>
@@ -5029,10 +5044,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514877</v>
+        <v>514881</v>
       </c>
       <c r="R39" t="n">
-        <v>7128689</v>
+        <v>7128694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5091,7 +5106,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120473800</v>
+        <v>120472732</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -5132,14 +5147,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515084</v>
+        <v>514834</v>
       </c>
       <c r="R40" t="n">
-        <v>7128716</v>
+        <v>7128590</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5203,10 +5218,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120472276</v>
+        <v>120471013</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5219,21 +5234,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5243,13 +5258,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514855</v>
+        <v>514711</v>
       </c>
       <c r="R41" t="n">
-        <v>7128420</v>
+        <v>7128463</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5279,11 +5294,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5310,10 +5320,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120472115</v>
+        <v>120471120</v>
       </c>
       <c r="B42" t="n">
-        <v>79652</v>
+        <v>90576</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5322,25 +5332,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5350,13 +5360,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514793</v>
+        <v>514749</v>
       </c>
       <c r="R42" t="n">
-        <v>7128431</v>
+        <v>7128456</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5412,10 +5422,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120471937</v>
+        <v>120471755</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5428,21 +5438,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5452,10 +5462,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514784</v>
+        <v>514726</v>
       </c>
       <c r="R43" t="n">
-        <v>7128441</v>
+        <v>7128427</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5514,10 +5524,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120471856</v>
+        <v>120471937</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5530,21 +5540,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5554,13 +5564,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514760</v>
+        <v>514784</v>
       </c>
       <c r="R44" t="n">
-        <v>7128399</v>
+        <v>7128441</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5616,10 +5626,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120471315</v>
+        <v>120473466</v>
       </c>
       <c r="B45" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5632,42 +5642,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514757</v>
+        <v>514969</v>
       </c>
       <c r="R45" t="n">
-        <v>7128439</v>
+        <v>7128668</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5723,10 +5728,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120472156</v>
+        <v>120471856</v>
       </c>
       <c r="B46" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5739,21 +5744,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5763,10 +5768,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514822</v>
+        <v>514760</v>
       </c>
       <c r="R46" t="n">
-        <v>7128428</v>
+        <v>7128399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5825,10 +5830,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120473097</v>
+        <v>120471298</v>
       </c>
       <c r="B47" t="n">
-        <v>79624</v>
+        <v>91370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5841,21 +5846,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>2014</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5865,13 +5870,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514881</v>
+        <v>514758</v>
       </c>
       <c r="R47" t="n">
-        <v>7128694</v>
+        <v>7128446</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5927,7 +5932,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120473133</v>
+        <v>120473868</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5963,14 +5968,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514883</v>
+        <v>515087</v>
       </c>
       <c r="R48" t="n">
-        <v>7128696</v>
+        <v>7128736</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6034,10 +6039,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120471114</v>
+        <v>120472650</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,25 +6051,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6074,13 +6079,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514743</v>
+        <v>514823</v>
       </c>
       <c r="R49" t="n">
-        <v>7128447</v>
+        <v>7128562</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6136,10 +6141,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120471755</v>
+        <v>120473043</v>
       </c>
       <c r="B50" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6152,21 +6157,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6176,10 +6181,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514726</v>
+        <v>514860</v>
       </c>
       <c r="R50" t="n">
-        <v>7128427</v>
+        <v>7128698</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6238,10 +6243,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120471204</v>
+        <v>120473036</v>
       </c>
       <c r="B51" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6250,25 +6255,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6278,13 +6283,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514761</v>
+        <v>514863</v>
       </c>
       <c r="R51" t="n">
-        <v>7128451</v>
+        <v>7128699</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6340,10 +6345,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120473562</v>
+        <v>120471334</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6356,37 +6361,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515029</v>
+        <v>514745</v>
       </c>
       <c r="R52" t="n">
-        <v>7128693</v>
+        <v>7128436</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6416,11 +6421,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -4377,10 +4377,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120473562</v>
+        <v>120471187</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,37 +4393,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515029</v>
+        <v>514760</v>
       </c>
       <c r="R33" t="n">
-        <v>7128693</v>
+        <v>7128455</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4453,11 +4453,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4484,10 +4479,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120471187</v>
+        <v>120472276</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4500,21 +4495,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4524,10 +4519,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514760</v>
+        <v>514855</v>
       </c>
       <c r="R34" t="n">
-        <v>7128455</v>
+        <v>7128420</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4560,6 +4555,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4586,7 +4586,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120472276</v>
+        <v>120473562</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4622,17 +4622,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514855</v>
+        <v>515029</v>
       </c>
       <c r="R35" t="n">
-        <v>7128420</v>
+        <v>7128693</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120471315</v>
+        <v>120473097</v>
       </c>
       <c r="B36" t="n">
-        <v>57473</v>
+        <v>79624</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4709,42 +4709,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514757</v>
+        <v>514881</v>
       </c>
       <c r="R36" t="n">
-        <v>7128439</v>
+        <v>7128694</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4800,10 +4795,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120472115</v>
+        <v>120471315</v>
       </c>
       <c r="B37" t="n">
-        <v>79652</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4812,41 +4807,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514793</v>
+        <v>514757</v>
       </c>
       <c r="R37" t="n">
-        <v>7128431</v>
+        <v>7128439</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120471204</v>
+        <v>120472115</v>
       </c>
       <c r="B38" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4918,21 +4918,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514761</v>
+        <v>514793</v>
       </c>
       <c r="R38" t="n">
-        <v>7128451</v>
+        <v>7128431</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5004,10 +5004,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473097</v>
+        <v>120471204</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5016,25 +5016,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5044,13 +5044,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514881</v>
+        <v>514761</v>
       </c>
       <c r="R39" t="n">
-        <v>7128694</v>
+        <v>7128451</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120471937</v>
+        <v>120473466</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5560,14 +5560,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514784</v>
+        <v>514969</v>
       </c>
       <c r="R44" t="n">
-        <v>7128441</v>
+        <v>7128668</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5626,7 +5626,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473466</v>
+        <v>120471937</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5662,14 +5662,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514969</v>
+        <v>514784</v>
       </c>
       <c r="R45" t="n">
-        <v>7128668</v>
+        <v>7128441</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>

--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -3225,7 +3225,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120473051</v>
+        <v>120471208</v>
       </c>
       <c r="B22" t="n">
         <v>79658</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514862</v>
+        <v>514759</v>
       </c>
       <c r="R22" t="n">
-        <v>7128700</v>
+        <v>7128445</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120473800</v>
+        <v>120471334</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3343,42 +3343,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515084</v>
+        <v>514745</v>
       </c>
       <c r="R23" t="n">
-        <v>7128716</v>
+        <v>7128436</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3408,11 +3403,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,10 +3429,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120471864</v>
+        <v>120471187</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3455,21 +3445,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3479,13 +3469,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514759</v>
+        <v>514760</v>
       </c>
       <c r="R24" t="n">
-        <v>7128395</v>
+        <v>7128455</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3541,10 +3531,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120471114</v>
+        <v>120471315</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3553,41 +3543,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514743</v>
+        <v>514757</v>
       </c>
       <c r="R25" t="n">
-        <v>7128447</v>
+        <v>7128439</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3643,7 +3638,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120473819</v>
+        <v>120472732</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3677,19 +3672,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515087</v>
+        <v>514834</v>
       </c>
       <c r="R26" t="n">
-        <v>7128729</v>
+        <v>7128590</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,7 +3750,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120472288</v>
+        <v>120473800</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3784,19 +3784,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514859</v>
+        <v>515084</v>
       </c>
       <c r="R27" t="n">
-        <v>7128434</v>
+        <v>7128716</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3830,7 +3835,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3857,10 +3862,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120473133</v>
+        <v>120472156</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3873,21 +3878,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3897,10 +3902,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514883</v>
+        <v>514822</v>
       </c>
       <c r="R28" t="n">
-        <v>7128696</v>
+        <v>7128428</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3933,11 +3938,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120471208</v>
+        <v>120473097</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4004,13 +4004,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514759</v>
+        <v>514881</v>
       </c>
       <c r="R29" t="n">
-        <v>7128445</v>
+        <v>7128694</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120472156</v>
+        <v>120471298</v>
       </c>
       <c r="B30" t="n">
-        <v>78279</v>
+        <v>91370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4082,21 +4082,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>2014</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514822</v>
+        <v>514758</v>
       </c>
       <c r="R30" t="n">
-        <v>7128428</v>
+        <v>7128446</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120473441</v>
+        <v>120473466</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514964</v>
+        <v>514969</v>
       </c>
       <c r="R31" t="n">
-        <v>7128671</v>
+        <v>7128668</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4244,11 +4244,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4275,10 +4270,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120473146</v>
+        <v>120473133</v>
       </c>
       <c r="B32" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4291,21 +4286,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4315,10 +4310,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514877</v>
+        <v>514883</v>
       </c>
       <c r="R32" t="n">
-        <v>7128689</v>
+        <v>7128696</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4351,6 +4346,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4377,10 +4377,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120471187</v>
+        <v>120472650</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514760</v>
+        <v>514823</v>
       </c>
       <c r="R33" t="n">
-        <v>7128455</v>
+        <v>7128562</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120472276</v>
+        <v>120471120</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4495,21 +4495,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514855</v>
+        <v>514749</v>
       </c>
       <c r="R34" t="n">
-        <v>7128420</v>
+        <v>7128456</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4555,11 +4555,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4586,10 +4581,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120473562</v>
+        <v>120471937</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4602,34 +4597,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>515029</v>
+        <v>514784</v>
       </c>
       <c r="R35" t="n">
-        <v>7128693</v>
+        <v>7128441</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4662,11 +4657,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4693,7 +4683,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473097</v>
+        <v>120473146</v>
       </c>
       <c r="B36" t="n">
         <v>79624</v>
@@ -4733,10 +4723,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514881</v>
+        <v>514877</v>
       </c>
       <c r="R36" t="n">
-        <v>7128694</v>
+        <v>7128689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4795,10 +4785,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120471315</v>
+        <v>120473051</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>79658</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4807,46 +4797,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514757</v>
+        <v>514862</v>
       </c>
       <c r="R37" t="n">
-        <v>7128439</v>
+        <v>7128700</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4902,10 +4887,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120472115</v>
+        <v>120471856</v>
       </c>
       <c r="B38" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4914,25 +4899,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4942,13 +4927,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514793</v>
+        <v>514760</v>
       </c>
       <c r="R38" t="n">
-        <v>7128431</v>
+        <v>7128399</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5004,10 +4989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120471204</v>
+        <v>120473036</v>
       </c>
       <c r="B39" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5016,25 +5001,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5044,13 +5029,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514761</v>
+        <v>514863</v>
       </c>
       <c r="R39" t="n">
-        <v>7128451</v>
+        <v>7128699</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5106,10 +5091,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120472732</v>
+        <v>120471114</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5118,46 +5103,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514834</v>
+        <v>514743</v>
       </c>
       <c r="R40" t="n">
-        <v>7128590</v>
+        <v>7128447</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5187,11 +5167,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5218,10 +5193,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120471013</v>
+        <v>120472115</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5230,25 +5205,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5258,10 +5233,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514711</v>
+        <v>514793</v>
       </c>
       <c r="R41" t="n">
-        <v>7128463</v>
+        <v>7128431</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5320,10 +5295,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120471120</v>
+        <v>120473819</v>
       </c>
       <c r="B42" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5336,34 +5311,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514749</v>
+        <v>515087</v>
       </c>
       <c r="R42" t="n">
-        <v>7128456</v>
+        <v>7128729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5396,6 +5371,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5422,10 +5402,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120471755</v>
+        <v>120473441</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5438,37 +5418,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514726</v>
+        <v>514964</v>
       </c>
       <c r="R43" t="n">
-        <v>7128427</v>
+        <v>7128671</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5498,6 +5478,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5524,10 +5509,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120473466</v>
+        <v>120472276</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5540,37 +5525,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514969</v>
+        <v>514855</v>
       </c>
       <c r="R44" t="n">
-        <v>7128668</v>
+        <v>7128420</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5600,6 +5585,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5626,10 +5616,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120471937</v>
+        <v>120471755</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5642,21 +5632,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5666,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514784</v>
+        <v>514726</v>
       </c>
       <c r="R45" t="n">
-        <v>7128441</v>
+        <v>7128427</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5728,10 +5718,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120471856</v>
+        <v>120471013</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5744,21 +5734,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5768,13 +5758,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514760</v>
+        <v>514711</v>
       </c>
       <c r="R46" t="n">
-        <v>7128399</v>
+        <v>7128463</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5830,10 +5820,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120471298</v>
+        <v>120473562</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5846,34 +5836,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2014</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514758</v>
+        <v>515029</v>
       </c>
       <c r="R47" t="n">
-        <v>7128446</v>
+        <v>7128693</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5906,6 +5896,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5932,10 +5927,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120473868</v>
+        <v>120471204</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5944,41 +5939,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515087</v>
+        <v>514761</v>
       </c>
       <c r="R48" t="n">
-        <v>7128736</v>
+        <v>7128451</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6008,11 +6003,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6039,10 +6029,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120472650</v>
+        <v>120473043</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6055,21 +6045,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6079,10 +6069,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514823</v>
+        <v>514860</v>
       </c>
       <c r="R49" t="n">
-        <v>7128562</v>
+        <v>7128698</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6141,10 +6131,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120473043</v>
+        <v>120472288</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6157,21 +6147,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6181,13 +6171,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514860</v>
+        <v>514859</v>
       </c>
       <c r="R50" t="n">
-        <v>7128698</v>
+        <v>7128434</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6217,6 +6207,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6243,10 +6238,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120473036</v>
+        <v>120473868</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6259,34 +6254,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514863</v>
+        <v>515087</v>
       </c>
       <c r="R51" t="n">
-        <v>7128699</v>
+        <v>7128736</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6319,6 +6314,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6345,10 +6345,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120471334</v>
+        <v>120471864</v>
       </c>
       <c r="B52" t="n">
-        <v>79624</v>
+        <v>79160</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6361,21 +6361,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6385,13 +6385,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514745</v>
+        <v>514759</v>
       </c>
       <c r="R52" t="n">
-        <v>7128436</v>
+        <v>7128395</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -3225,10 +3225,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120471208</v>
+        <v>120471937</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3237,20 +3237,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514759</v>
+        <v>514784</v>
       </c>
       <c r="R22" t="n">
-        <v>7128445</v>
+        <v>7128441</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120471334</v>
+        <v>120473868</v>
       </c>
       <c r="B23" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3343,34 +3343,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514745</v>
+        <v>515087</v>
       </c>
       <c r="R23" t="n">
-        <v>7128436</v>
+        <v>7128736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3403,6 +3403,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3429,10 +3434,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120471187</v>
+        <v>120471204</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3441,25 +3446,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3469,13 +3474,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514760</v>
+        <v>514761</v>
       </c>
       <c r="R24" t="n">
-        <v>7128455</v>
+        <v>7128451</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3531,10 +3536,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120471315</v>
+        <v>120472276</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3547,42 +3552,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514757</v>
+        <v>514855</v>
       </c>
       <c r="R25" t="n">
-        <v>7128439</v>
+        <v>7128420</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3612,6 +3612,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3638,7 +3643,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120472732</v>
+        <v>120473800</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3679,14 +3684,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514834</v>
+        <v>515084</v>
       </c>
       <c r="R26" t="n">
-        <v>7128590</v>
+        <v>7128716</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3750,10 +3755,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120473800</v>
+        <v>120471864</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3766,39 +3771,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515084</v>
+        <v>514759</v>
       </c>
       <c r="R27" t="n">
-        <v>7128716</v>
+        <v>7128395</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3831,11 +3831,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3862,10 +3857,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120472156</v>
+        <v>120472650</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3878,21 +3873,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3902,13 +3897,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514822</v>
+        <v>514823</v>
       </c>
       <c r="R28" t="n">
-        <v>7128428</v>
+        <v>7128562</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4066,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120471298</v>
+        <v>120473051</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>79658</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4078,25 +4073,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2014</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514758</v>
+        <v>514862</v>
       </c>
       <c r="R30" t="n">
-        <v>7128446</v>
+        <v>7128700</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4168,7 +4163,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120473466</v>
+        <v>120471013</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -4204,14 +4199,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514969</v>
+        <v>514711</v>
       </c>
       <c r="R31" t="n">
-        <v>7128668</v>
+        <v>7128463</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4270,10 +4265,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120473133</v>
+        <v>120473036</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4286,21 +4281,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4310,10 +4305,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514883</v>
+        <v>514863</v>
       </c>
       <c r="R32" t="n">
-        <v>7128696</v>
+        <v>7128699</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4346,11 +4341,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4377,10 +4367,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120472650</v>
+        <v>120471298</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>91370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,21 +4383,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4417,10 +4407,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514823</v>
+        <v>514758</v>
       </c>
       <c r="R33" t="n">
-        <v>7128562</v>
+        <v>7128446</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4479,10 +4469,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120471120</v>
+        <v>120472732</v>
       </c>
       <c r="B34" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4495,37 +4485,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514749</v>
+        <v>514834</v>
       </c>
       <c r="R34" t="n">
-        <v>7128456</v>
+        <v>7128590</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4555,6 +4550,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4581,10 +4581,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120471937</v>
+        <v>120471120</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4597,21 +4597,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514784</v>
+        <v>514749</v>
       </c>
       <c r="R35" t="n">
-        <v>7128441</v>
+        <v>7128456</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473146</v>
+        <v>120472156</v>
       </c>
       <c r="B36" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514877</v>
+        <v>514822</v>
       </c>
       <c r="R36" t="n">
-        <v>7128689</v>
+        <v>7128428</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120473051</v>
+        <v>120473466</v>
       </c>
       <c r="B37" t="n">
-        <v>79658</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4797,20 +4797,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4821,14 +4821,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514862</v>
+        <v>514969</v>
       </c>
       <c r="R37" t="n">
-        <v>7128700</v>
+        <v>7128668</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120471856</v>
+        <v>120472115</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4899,25 +4899,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514760</v>
+        <v>514793</v>
       </c>
       <c r="R38" t="n">
-        <v>7128399</v>
+        <v>7128431</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473036</v>
+        <v>120473146</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514863</v>
+        <v>514877</v>
       </c>
       <c r="R39" t="n">
-        <v>7128699</v>
+        <v>7128689</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120471114</v>
+        <v>120473441</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,38 +5103,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514743</v>
+        <v>514964</v>
       </c>
       <c r="R40" t="n">
-        <v>7128447</v>
+        <v>7128671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,6 +5167,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5193,10 +5198,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120472115</v>
+        <v>120473819</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5205,41 +5210,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514793</v>
+        <v>515087</v>
       </c>
       <c r="R41" t="n">
-        <v>7128431</v>
+        <v>7128729</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5269,6 +5274,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5295,10 +5305,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120473819</v>
+        <v>120471856</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5311,34 +5321,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515087</v>
+        <v>514760</v>
       </c>
       <c r="R42" t="n">
-        <v>7128729</v>
+        <v>7128399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5371,11 +5381,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5402,10 +5407,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120473441</v>
+        <v>120471755</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5418,37 +5423,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514964</v>
+        <v>514726</v>
       </c>
       <c r="R43" t="n">
-        <v>7128671</v>
+        <v>7128427</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5478,11 +5483,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5509,7 +5509,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120472276</v>
+        <v>120473562</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5545,17 +5545,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514855</v>
+        <v>515029</v>
       </c>
       <c r="R44" t="n">
-        <v>7128420</v>
+        <v>7128693</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120471755</v>
+        <v>120472288</v>
       </c>
       <c r="B45" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514726</v>
+        <v>514859</v>
       </c>
       <c r="R45" t="n">
-        <v>7128427</v>
+        <v>7128434</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5692,6 +5692,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5718,10 +5723,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120471013</v>
+        <v>120471114</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5730,25 +5735,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5758,13 +5763,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514711</v>
+        <v>514743</v>
       </c>
       <c r="R46" t="n">
-        <v>7128463</v>
+        <v>7128447</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5820,10 +5825,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120473562</v>
+        <v>120471208</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>79658</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5832,38 +5837,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515029</v>
+        <v>514759</v>
       </c>
       <c r="R47" t="n">
-        <v>7128693</v>
+        <v>7128445</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5896,11 +5901,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,10 +5927,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120471204</v>
+        <v>120471315</v>
       </c>
       <c r="B48" t="n">
-        <v>79659</v>
+        <v>57473</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5939,41 +5939,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514761</v>
+        <v>514757</v>
       </c>
       <c r="R48" t="n">
-        <v>7128451</v>
+        <v>7128439</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6131,7 +6136,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120472288</v>
+        <v>120473133</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -6171,10 +6176,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514859</v>
+        <v>514883</v>
       </c>
       <c r="R50" t="n">
-        <v>7128434</v>
+        <v>7128696</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,10 +6243,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120473868</v>
+        <v>120471334</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6254,34 +6259,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515087</v>
+        <v>514745</v>
       </c>
       <c r="R51" t="n">
-        <v>7128736</v>
+        <v>7128436</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6314,11 +6319,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6345,10 +6345,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120471864</v>
+        <v>120471187</v>
       </c>
       <c r="B52" t="n">
-        <v>79160</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6361,21 +6361,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6385,13 +6385,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514759</v>
+        <v>514760</v>
       </c>
       <c r="R52" t="n">
-        <v>7128395</v>
+        <v>7128455</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 35710-2020 artfynd.xlsx
+++ b/artfynd/A 35710-2020 artfynd.xlsx
@@ -5198,10 +5198,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120473819</v>
+        <v>120471856</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5214,34 +5214,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grundsundet, Grundsundet, Jmt</t>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515087</v>
+        <v>514760</v>
       </c>
       <c r="R41" t="n">
-        <v>7128729</v>
+        <v>7128399</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,11 +5274,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5305,10 +5300,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120471856</v>
+        <v>120473819</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5321,34 +5316,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+          <t>Grundsundet, Grundsundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514760</v>
+        <v>515087</v>
       </c>
       <c r="R42" t="n">
-        <v>7128399</v>
+        <v>7128729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5381,6 +5376,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6034,10 +6034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120473043</v>
+        <v>120473133</v>
       </c>
       <c r="B49" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6074,13 +6074,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514860</v>
+        <v>514883</v>
       </c>
       <c r="R49" t="n">
-        <v>7128698</v>
+        <v>7128696</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6110,6 +6110,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6136,10 +6141,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120473133</v>
+        <v>120473043</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6152,21 +6157,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6176,13 +6181,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514883</v>
+        <v>514860</v>
       </c>
       <c r="R50" t="n">
-        <v>7128696</v>
+        <v>7128698</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6212,11 +6217,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6243,10 +6243,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120471334</v>
+        <v>120471187</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6259,21 +6259,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514745</v>
+        <v>514760</v>
       </c>
       <c r="R51" t="n">
-        <v>7128436</v>
+        <v>7128455</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6345,10 +6345,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120471187</v>
+        <v>120471334</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6361,21 +6361,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6385,10 +6385,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514760</v>
+        <v>514745</v>
       </c>
       <c r="R52" t="n">
-        <v>7128455</v>
+        <v>7128436</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
